--- a/experiments/results/densenet101/CIFAR-10/ASH/adaptive/avg/results.xlsx
+++ b/experiments/results/densenet101/CIFAR-10/ASH/adaptive/avg/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -1156,6 +1156,55 @@
       <c r="O16" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=90,react_th=None,scale_th=0.5,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>98.61</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>99.22</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>96.62</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>99.15000000000001</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>97.54000000000001</v>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=90,react_th=None,scale_th=0.05,type=avg</t>
         </is>
       </c>
     </row>
